--- a/config/solvency_validation_rules.xlsx
+++ b/config/solvency_validation_rules.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勾稽规则" sheetId="1" r:id="Re15ffc7e18754bd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勾稽规则" sheetId="1" r:id="R1234044d27864f3e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36,7 +36,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -51,6 +51,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1E49E2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC6E8F5"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -88,7 +98,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -117,6 +127,8 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -538,13 +550,59 @@
         <x:v>最低资本=量化风险最低资本+控制风险最低资本+附加资本</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>DUPLICATE_ACTUAL_CAPITAL</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>实际资本跨表重复值一致</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>本季度末数|上季度末数|下季度末预测数|期末数|期初数</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>万元</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>偿付能力主表中的实际资本，应与实际资本表中的实际资本总额保持一致</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="15" t="str">
+        <x:v>DUPLICATE_MINIMUM_CAPITAL</x:v>
+      </x:c>
+      <x:c r="B12" s="15" t="str">
+        <x:v>最低资本跨表重复值一致</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="str">
+        <x:v>本季度末数|上季度末数|下季度末预测数|期末数|期初数</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="str">
+        <x:v>万元</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="str">
+        <x:v>偿付能力主表中的最低资本，应与最低资本表中的最低资本合计保持一致</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R328530e27bac4650"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e6c563fd3204b60"/>
   </x:tableParts>
 </x:worksheet>
 </file>